--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OH!TELS ULB.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OH!TELS ULB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0081</v>
+        <v>32.4993</v>
       </c>
       <c r="E2" t="n">
-        <v>32.0081</v>
+        <v>31.4482</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.0509</v>
       </c>
       <c r="G2" t="n">
-        <v>32.0081</v>
+        <v>14.5367</v>
       </c>
       <c r="H2" t="n">
-        <v>15.1332</v>
+        <v>10.3758</v>
       </c>
       <c r="I2" t="n">
-        <v>16.8749</v>
+        <v>4.160699999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>32.0081</v>
+        <v>51.2993</v>
       </c>
       <c r="K2" t="n">
-        <v>15.1332</v>
+        <v>35.6618</v>
       </c>
       <c r="L2" t="n">
-        <v>16.8749</v>
+        <v>15.6371</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-36.7622</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-25.2859</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-11.4765</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-21.2098</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-77.10890000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>55.8988</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-12.0796</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-7.418299999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-4.6619</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>51.2518</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>64.67570000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-13.4239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>21.0226</v>
+        <v>32.0081</v>
       </c>
       <c r="E3" t="n">
-        <v>20.5164</v>
+        <v>32.0081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5061999999999998</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>14.5367</v>
+        <v>32.0081</v>
       </c>
       <c r="H3" t="n">
-        <v>10.3758</v>
+        <v>15.1332</v>
       </c>
       <c r="I3" t="n">
-        <v>4.160699999999999</v>
+        <v>16.8749</v>
       </c>
       <c r="J3" t="n">
-        <v>51.2993</v>
+        <v>32.0081</v>
       </c>
       <c r="K3" t="n">
-        <v>35.6618</v>
+        <v>15.1332</v>
       </c>
       <c r="L3" t="n">
-        <v>15.6371</v>
+        <v>16.8749</v>
       </c>
       <c r="M3" t="n">
-        <v>-36.7622</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-25.2859</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.4765</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-21.2098</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-77.10890000000001</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8988</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-23.5562</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-18.3501</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.206300000000001</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>51.2518</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>64.67570000000001</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.4239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8191</v>
+        <v>6.021500000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5691</v>
+        <v>23.9003</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.7507</v>
+        <v>-17.8787</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.9664</v>
+        <v>14.5609</v>
       </c>
       <c r="H4" t="n">
-        <v>4.288600000000001</v>
+        <v>25.8755</v>
       </c>
       <c r="I4" t="n">
-        <v>-8.2552</v>
+        <v>-11.3147</v>
       </c>
       <c r="J4" t="n">
-        <v>17.5421</v>
+        <v>34.2186</v>
       </c>
       <c r="K4" t="n">
-        <v>17.266</v>
+        <v>34.9716</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2763000000000001</v>
+        <v>-0.7531000000000002</v>
       </c>
       <c r="M4" t="n">
-        <v>-21.5086</v>
+        <v>-19.6576</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.9776</v>
+        <v>-9.095699999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.5311</v>
+        <v>-10.5619</v>
       </c>
       <c r="P4" t="n">
-        <v>12.6861</v>
+        <v>-6.5412</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.8754</v>
+        <v>-35.4816</v>
       </c>
       <c r="R4" t="n">
-        <v>26.5616</v>
+        <v>28.9405</v>
       </c>
       <c r="S4" t="n">
-        <v>16.8564</v>
+        <v>-7.443000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>10.5268</v>
+        <v>-2.2881</v>
       </c>
       <c r="U4" t="n">
-        <v>6.329499999999999</v>
+        <v>-5.1552</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.7571</v>
+        <v>5.4451</v>
       </c>
       <c r="W4" t="n">
-        <v>4.375900000000001</v>
+        <v>27.4517</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.1328</v>
+        <v>-22.007</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>5.406999999999998</v>
+        <v>2.625400000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>26.4738</v>
+        <v>11.4512</v>
       </c>
       <c r="F5" t="n">
-        <v>-21.0664</v>
+        <v>-8.8255</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5609</v>
+        <v>-3.9664</v>
       </c>
       <c r="H5" t="n">
-        <v>25.8755</v>
+        <v>4.288600000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.3147</v>
+        <v>-8.2552</v>
       </c>
       <c r="J5" t="n">
-        <v>34.2186</v>
+        <v>17.5421</v>
       </c>
       <c r="K5" t="n">
-        <v>34.9716</v>
+        <v>17.266</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7531000000000002</v>
+        <v>0.2763000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-19.6576</v>
+        <v>-21.5086</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.095699999999999</v>
+        <v>-12.9776</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.5619</v>
+        <v>-8.5311</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.5412</v>
+        <v>12.6861</v>
       </c>
       <c r="Q5" t="n">
-        <v>-35.4816</v>
+        <v>-13.8754</v>
       </c>
       <c r="R5" t="n">
-        <v>28.9405</v>
+        <v>26.5616</v>
       </c>
       <c r="S5" t="n">
-        <v>-8.057500000000001</v>
+        <v>5.663</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2855000000000001</v>
+        <v>3.4086</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.3428</v>
+        <v>2.2544</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4451</v>
+        <v>-11.7571</v>
       </c>
       <c r="W5" t="n">
-        <v>27.4517</v>
+        <v>4.375900000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.007</v>
+        <v>-16.1328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>A. MATEOS PEÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8706</v>
+        <v>0.6027</v>
       </c>
       <c r="E6" t="n">
-        <v>12.0613</v>
+        <v>0.6027</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.190900000000001</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.482999999999999</v>
+        <v>0.6027</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.3767</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1063</v>
+        <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>9.1233</v>
+        <v>0.6027</v>
       </c>
       <c r="K6" t="n">
-        <v>7.316599999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8068</v>
+        <v>0.6027</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.6063</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.6931</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.9132</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.947</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-23.3899</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>29.337</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>11.8156</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>12.8842</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0685</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.4089</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>13.4445</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.8527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MATEOS PEÑA</t>
+          <t>M. AGUILERA GIL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6027</v>
+        <v>0.2932</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6027</v>
+        <v>-0.7884</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.0816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6027</v>
+        <v>-1.5468</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.2687</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6027</v>
+        <v>-1.8155</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6027</v>
+        <v>-1.8359</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6027</v>
+        <v>-1.957</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.2892</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.1476</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1415</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.1894</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1894</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.6268</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1596</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.4672</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2775</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. AGUILERA GIL</t>
+          <t>I. POYATOS GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1632</v>
+        <v>-0.453</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9922000000000001</v>
+        <v>-1.1893</v>
       </c>
       <c r="F8" t="n">
-        <v>0.829</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5468</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2687</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8155</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8359</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.957</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2892</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1476</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1415</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1894</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1894</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0832</v>
+        <v>-0.1358</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7199</v>
+        <v>-0.1358</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2775</v>
+        <v>0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. POYATOS GARCIA</t>
+          <t>J. COCA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.453</v>
+        <v>-3.2772</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1893</v>
+        <v>-1.7133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7364000000000001</v>
+        <v>-1.5639</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1.4547</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.7869</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.6677</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.4748</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.8071</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.6677</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1358</v>
+        <v>0.1597</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.2487</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1358</v>
+        <v>-0.089</v>
       </c>
       <c r="V9" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. COCA LOPEZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9997</v>
+        <v>-5.3315</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4077</v>
+        <v>2.708400000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5919</v>
+        <v>-8.040099999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4547</v>
+        <v>-7.482999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7869</v>
+        <v>-5.3767</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6677</v>
+        <v>-2.1063</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0202</v>
+        <v>9.1233</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>7.316599999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8068</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4748</v>
+        <v>-16.6063</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8071</v>
+        <v>-12.6931</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6677</v>
+        <v>-3.9132</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9822</v>
+        <v>5.947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-23.3899</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>29.337</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4372</v>
+        <v>2.6133</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5543</v>
+        <v>3.5315</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1171</v>
+        <v>-0.9175999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-6.4089</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>13.4445</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-19.8527</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2741</v>
+        <v>-6.218299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.653</v>
+        <v>-6.118500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3788</v>
+        <v>-0.09980000000000033</v>
       </c>
       <c r="G11" t="n">
         <v>-1.742</v>
@@ -1312,13 +1312,13 @@
         <v>18.4347</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2749</v>
+        <v>-4.219200000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6813000000000002</v>
+        <v>-2.1467</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5938</v>
+        <v>-2.072</v>
       </c>
       <c r="V11" t="n">
         <v>-4.6181</v>
@@ -1345,13 +1345,13 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.9924</v>
+        <v>-8.083600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7034</v>
+        <v>-9.1317</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7112000000000002</v>
+        <v>1.0481</v>
       </c>
       <c r="G12" t="n">
         <v>-9.4313</v>
@@ -1390,13 +1390,13 @@
         <v>3.7662</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0696</v>
+        <v>-1.1609</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8038</v>
+        <v>-0.2318000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2661</v>
+        <v>-0.9292</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.571300000000001</v>
+        <v>-10.2312</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.7003</v>
+        <v>-11.1637</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1289</v>
+        <v>0.9325000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-5.2942</v>
@@ -1468,13 +1468,13 @@
         <v>5.153499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01560000000000006</v>
+        <v>-0.6442999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04810000000000003</v>
+        <v>-0.4151</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03250000000000003</v>
+        <v>-0.2288999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.9053</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.7613</v>
+        <v>-13.8899</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.066000000000001</v>
+        <v>-7.0405</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.6957</v>
+        <v>-6.8492</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.298</v>
+        <v>-3.3354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5999999999999999</v>
+        <v>0.5617000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.8979</v>
+        <v>-3.8975</v>
       </c>
       <c r="J14" t="n">
-        <v>11.6975</v>
+        <v>1.1449</v>
       </c>
       <c r="K14" t="n">
-        <v>12.2455</v>
+        <v>1.3874</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5483000000000002</v>
+        <v>-0.2423</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.9955</v>
+        <v>-4.4802</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.6458</v>
+        <v>-0.8252999999999997</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.3497</v>
+        <v>-3.6548</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.721400000000001</v>
+        <v>-1.1894</v>
       </c>
       <c r="Q14" t="n">
-        <v>-36.4728</v>
+        <v>-10.1091</v>
       </c>
       <c r="R14" t="n">
-        <v>27.7513</v>
+        <v>8.92</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2881</v>
+        <v>-0.3028</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1135</v>
+        <v>0.7168000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1744</v>
+        <v>-1.0196</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.0297</v>
+        <v>-9.0626</v>
       </c>
       <c r="W14" t="n">
-        <v>14.5963</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.6258</v>
+        <v>-10.2697</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.7872</v>
+        <v>-21.2522</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.735200000000001</v>
+        <v>-10.1632</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.052099999999999</v>
+        <v>-11.0888</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.3354</v>
+        <v>-8.298</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5617000000000001</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.8975</v>
+        <v>-8.8979</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1449</v>
+        <v>11.6975</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3874</v>
+        <v>12.2455</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2423</v>
+        <v>-0.5483000000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.4802</v>
+        <v>-19.9955</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8252999999999997</v>
+        <v>-11.6458</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.6548</v>
+        <v>-8.3497</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1894</v>
+        <v>-8.721400000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10.1091</v>
+        <v>-36.4728</v>
       </c>
       <c r="R15" t="n">
-        <v>8.92</v>
+        <v>27.7513</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.2002</v>
+        <v>0.7973000000000005</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9776</v>
+        <v>0.01640000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.2225</v>
+        <v>0.781</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.0626</v>
+        <v>-5.0297</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>14.5963</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.2697</v>
+        <v>-19.6258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-32.7697</v>
+        <v>-29.0968</v>
       </c>
       <c r="E16" t="n">
-        <v>-26.2522</v>
+        <v>-18.6065</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.5177</v>
+        <v>-10.4903</v>
       </c>
       <c r="G16" t="n">
-        <v>6.758699999999999</v>
+        <v>-7.8535</v>
       </c>
       <c r="H16" t="n">
-        <v>12.5521</v>
+        <v>11.0856</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.793200000000001</v>
+        <v>-18.9391</v>
       </c>
       <c r="J16" t="n">
-        <v>34.2846</v>
+        <v>16.9253</v>
       </c>
       <c r="K16" t="n">
-        <v>29.5783</v>
+        <v>27.6344</v>
       </c>
       <c r="L16" t="n">
-        <v>4.706</v>
+        <v>-10.7092</v>
       </c>
       <c r="M16" t="n">
-        <v>-27.5256</v>
+        <v>-24.7789</v>
       </c>
       <c r="N16" t="n">
-        <v>-17.0265</v>
+        <v>-16.5489</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.4992</v>
+        <v>-8.229900000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-25.9671</v>
+        <v>-11.1006</v>
       </c>
       <c r="Q16" t="n">
-        <v>-65.8099</v>
+        <v>-51.1413</v>
       </c>
       <c r="R16" t="n">
-        <v>39.8429</v>
+        <v>40.0411</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.834</v>
+        <v>-12.5428</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6463000000000001</v>
+        <v>-5.5399</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.1879</v>
+        <v>-7.0026</v>
       </c>
       <c r="V16" t="n">
-        <v>-9.727399999999999</v>
+        <v>2.4003</v>
       </c>
       <c r="W16" t="n">
-        <v>5.92</v>
+        <v>21.1497</v>
       </c>
       <c r="X16" t="n">
-        <v>-15.6473</v>
+        <v>-18.7494</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-43.1425</v>
+        <v>-36.3084</v>
       </c>
       <c r="E17" t="n">
-        <v>-28.2244</v>
+        <v>-29.1085</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.9182</v>
+        <v>-7.199899999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.8535</v>
+        <v>6.758699999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>11.0856</v>
+        <v>12.5521</v>
       </c>
       <c r="I17" t="n">
-        <v>-18.9391</v>
+        <v>-5.793200000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>16.9253</v>
+        <v>34.2846</v>
       </c>
       <c r="K17" t="n">
-        <v>27.6344</v>
+        <v>29.5783</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.7092</v>
+        <v>4.706</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.7789</v>
+        <v>-27.5256</v>
       </c>
       <c r="N17" t="n">
-        <v>-16.5489</v>
+        <v>-17.0265</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.229900000000001</v>
+        <v>-10.4992</v>
       </c>
       <c r="P17" t="n">
-        <v>-11.1006</v>
+        <v>-25.9671</v>
       </c>
       <c r="Q17" t="n">
-        <v>-51.1413</v>
+        <v>-65.8099</v>
       </c>
       <c r="R17" t="n">
-        <v>40.0411</v>
+        <v>39.8429</v>
       </c>
       <c r="S17" t="n">
-        <v>-26.5886</v>
+        <v>-7.3727</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.1576</v>
+        <v>-3.5027</v>
       </c>
       <c r="U17" t="n">
-        <v>-11.4309</v>
+        <v>-3.8699</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4003</v>
+        <v>-9.727399999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>21.1497</v>
+        <v>5.92</v>
       </c>
       <c r="X17" t="n">
-        <v>-18.7494</v>
+        <v>-15.6473</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-47.8564</v>
+        <v>-38.4496</v>
       </c>
       <c r="E18" t="n">
-        <v>-33.7186</v>
+        <v>-30.3083</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.1378</v>
+        <v>-8.1412</v>
       </c>
       <c r="G18" t="n">
         <v>-22.9242</v>
@@ -1858,13 +1858,13 @@
         <v>48.9612</v>
       </c>
       <c r="S18" t="n">
-        <v>-22.5309</v>
+        <v>-13.124</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.741899999999999</v>
+        <v>-6.3319</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.7889</v>
+        <v>-6.7926</v>
       </c>
       <c r="V18" t="n">
         <v>-4.7799</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-60.454</v>
+        <v>-46.3878</v>
       </c>
       <c r="E19" t="n">
-        <v>-39.573</v>
+        <v>-30.7865</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.8811</v>
+        <v>-15.601</v>
       </c>
       <c r="G19" t="n">
         <v>-45.1502</v>
@@ -1936,13 +1936,13 @@
         <v>42.6179</v>
       </c>
       <c r="S19" t="n">
-        <v>-21.0999</v>
+        <v>-7.0334</v>
       </c>
       <c r="T19" t="n">
-        <v>-14.0264</v>
+        <v>-5.2399</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.0734</v>
+        <v>-1.7937</v>
       </c>
       <c r="V19" t="n">
         <v>6.5889</v>
@@ -1969,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-168.4947</v>
+        <v>-144.9293</v>
       </c>
       <c r="E20" t="n">
-        <v>-63.9839</v>
+        <v>-53.9995</v>
       </c>
       <c r="F20" t="n">
-        <v>-104.512</v>
+        <v>-90.9289</v>
       </c>
       <c r="G20" t="n">
-        <v>-50.01259999999999</v>
+        <v>-50.0126</v>
       </c>
       <c r="H20" t="n">
         <v>46.2941</v>
@@ -1993,10 +1993,10 @@
         <v>207.7327</v>
       </c>
       <c r="L20" t="n">
-        <v>4.044900000000004</v>
+        <v>4.0449</v>
       </c>
       <c r="M20" t="n">
-        <v>-261.7900999999999</v>
+        <v>-261.7901000000001</v>
       </c>
       <c r="N20" t="n">
         <v>-161.4382</v>
@@ -2005,7 +2005,7 @@
         <v>-100.3514</v>
       </c>
       <c r="P20" t="n">
-        <v>-50.5465</v>
+        <v>-50.54650000000001</v>
       </c>
       <c r="Q20" t="n">
         <v>-428.1593</v>
@@ -2014,22 +2014,22 @@
         <v>377.6143000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-81.0179</v>
+        <v>-57.45200000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-35.33600000000001</v>
+        <v>-25.352</v>
       </c>
       <c r="U20" t="n">
-        <v>-45.6825</v>
+        <v>-32.0998</v>
       </c>
       <c r="V20" t="n">
-        <v>13.08200000000001</v>
+        <v>13.082</v>
       </c>
       <c r="W20" t="n">
         <v>187.7366</v>
       </c>
       <c r="X20" t="n">
-        <v>-174.654</v>
+        <v>-174.6540000000001</v>
       </c>
     </row>
   </sheetData>
